--- a/templates/WPS求购模板.xlsx
+++ b/templates/WPS求购模板.xlsx
@@ -169,7 +169,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -537,16 +537,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>WPS 求购表 · 简规</t>
+          <t>WPS 求购 · 怎么用</t>
         </is>
       </c>
     </row>
@@ -556,69 +556,76 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>管理员：复制「模板」→ 改名给买家 → 开编辑权限。</t>
+          <t>1. 打开云文档（链接由群主分享）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>买家：只改自己的表。填参考印刷 + 是否必须此版。</t>
+          <t>2. 找到名为「模板」的工作表</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>3. 在「模板」上【右键】→【创建副本】</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>列：系列 编号 语言 闪 必须 数量 备注</t>
+          <t>4. 把副本【重命名】成你自己的名字</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>语言：e=英 z=中 j=日 o=其他（空=e）</t>
+          <t>5. 只改自己的表：上方填昵称/城市/联系，下方填求购</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>闪：空/0=否  1=是</t>
+          <t>6. 若没有编辑权限 / 无法创建副本：联系 QQ 417592443 申请</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>必须：0=其他版本也可以  1=必须此印刷（空=0）</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>数量：空=1</t>
+          <t>列：系列 编号 语言 闪 必须 数量 备注</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>语言 e/z/j/o（空=e）  闪 0/1  必须 0=可替其他版 1=必须此版（空=0）</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>例：mh3 224 e 0 1 → 只要这一版</t>
+          <t>数量空=1。每天统一更新到网站。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>例：iko 185 e 0 0 → 以这张为参考，其他版本也行</t>
+      <c r="A14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>文档：https://www.kdocs.cn/l/cvvaN21e3gm8</t>
         </is>
       </c>
     </row>
@@ -653,10 +660,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>语言 e/z/j/o（空=e）｜闪 0/1（空=0）｜必须 0=可替其他版 1=必须此版（空=0）｜数量空=1</t>
+          <t>语言 e/z/j/o（空=e）｜闪 0/1｜必须 0=可替 1=必须此版（空=0）｜数量空=1｜无权限 QQ 417592443</t>
         </is>
       </c>
     </row>
@@ -782,7 +789,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>示例：可替，要2张</t>
+          <t>示例：可替</t>
         </is>
       </c>
     </row>
@@ -1465,10 +1472,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>语言 e/z/j/o（空=e）｜闪 0/1（空=0）｜必须 0=可替其他版 1=必须此版（空=0）｜数量空=1</t>
+          <t>语言 e/z/j/o（空=e）｜闪 0/1｜必须 0=可替 1=必须此版（空=0）｜数量空=1｜无权限 QQ 417592443</t>
         </is>
       </c>
     </row>
@@ -1578,64 +1585,42 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>msc</t>
+          <t>iko</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>185</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>e</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>可替其他印刷</t>
+          <t>任意版本</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>iko</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>任意版本</t>
-        </is>
-      </c>
+      <c r="A11" s="11" t="inlineStr"/>
+      <c r="B11" s="11" t="inlineStr"/>
+      <c r="C11" s="11" t="inlineStr"/>
+      <c r="D11" s="11" t="inlineStr"/>
+      <c r="E11" s="11" t="inlineStr"/>
+      <c r="F11" s="11" t="inlineStr"/>
+      <c r="G11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr"/>

--- a/templates/WPS求购模板.xlsx
+++ b/templates/WPS求购模板.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -556,76 +556,52 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1. 打开云文档（链接由群主分享）</t>
+          <t>1. 在「模板」上【右键】→【创建副本】</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2. 找到名为「模板」的工作表</t>
+          <t>2. 把副本【重命名】成你自己的名字</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3. 在「模板」上【右键】→【创建副本】</t>
+          <t>3. 只改自己的表：上方填昵称/城市/联系，下方填求购</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>4. 把副本【重命名】成你自己的名字</t>
+          <t>4. 若没有编辑权限 / 无法创建副本：联系 QQ 417592443 申请</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>5. 只改自己的表：上方填昵称/城市/联系，下方填求购</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>6. 若没有编辑权限 / 无法创建副本：联系 QQ 417592443 申请</t>
+          <t>列：系列 编号 语言 闪 必须 数量 备注</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>语言 e/z/j/o（空=e）  闪 0/1  必须 0=可替其他版 1=必须此版（空=0）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>列：系列 编号 语言 闪 必须 数量 备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>语言 e/z/j/o（空=e）  闪 0/1  必须 0=可替其他版 1=必须此版（空=0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
           <t>数量空=1。每天统一更新到网站。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>文档：https://www.kdocs.cn/l/cvvaN21e3gm8</t>
         </is>
       </c>
     </row>
